--- a/multiSchoolOutput/04_School_of_Health_in_Social_Science/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/04_School_of_Health_in_Social_Science/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1301,7 +1301,7 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0210_00_GFS1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1543,7 +1543,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1720,7 +1720,7 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0208_-1_B.1</t>
+          <t>0003_03_3.02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1897,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0335_05_5.3</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2074,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0228_11_11.10</t>
+          <t>0300_00_NG.01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0335_02_2.3</t>
+          <t>0335_01_1.16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2192,7 +2192,7 @@
         <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2251,7 +2251,7 @@
         <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0227_00_G.02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2310,7 +2310,7 @@
         <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0201_05_5.04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2369,7 +2369,7 @@
         <v>40</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2428,7 +2428,7 @@
         <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0201_02_2.12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2487,7 +2487,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tuesday 15:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2605,7 +2605,7 @@
         <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0112_00_G.01</t>
+          <t>0112_00_G.02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2782,7 +2782,7 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2824,12 +2824,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2841,7 +2841,7 @@
         <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2900,7 +2900,7 @@
         <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3018,7 +3018,7 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3077,7 +3077,7 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0335_00_G.09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3136,7 +3136,7 @@
         <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0311_01_1.26</t>
+          <t>0110_02_2.04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3195,7 +3195,7 @@
         <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3254,7 +3254,7 @@
         <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0201_05_5.04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3313,7 +3313,7 @@
         <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0226_-1_LG.10</t>
+          <t>0228_-1_LG.11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3372,7 +3372,7 @@
         <v>72</v>
       </c>
       <c r="F50" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3490,7 +3490,7 @@
         <v>52</v>
       </c>
       <c r="F52" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0310_00_G.02</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3549,7 +3549,7 @@
         <v>40</v>
       </c>
       <c r="F53" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3726,7 +3726,7 @@
         <v>6</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>6</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3827,12 +3827,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3844,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0008_03_3.451</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3962,7 +3962,7 @@
         <v>40</v>
       </c>
       <c r="F60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4021,7 +4021,7 @@
         <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0113_01_1.9</t>
+          <t>0210_00_GFS1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4139,7 +4139,7 @@
         <v>40</v>
       </c>
       <c r="F63" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4198,7 +4198,7 @@
         <v>80</v>
       </c>
       <c r="F64" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0450_01_1.40</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4316,7 +4316,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4375,7 +4375,7 @@
         <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4434,7 +4434,7 @@
         <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4493,7 +4493,7 @@
         <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4552,7 +4552,7 @@
         <v>6</v>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0112_00_G.02</t>
+          <t>0112_00_G.01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0226_-1_LG.10</t>
+          <t>0228_-1_LG.11</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0113_00_G.03</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4731,7 +4731,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4792,7 +4792,7 @@
         <v>8</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0008_03_3.451</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4853,7 +4853,7 @@
         <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0227_03_3.39</t>
+          <t>0003_00_G.03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5158,7 +5158,7 @@
         <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5202,12 +5202,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5402,7 +5402,7 @@
         <v>8</v>
       </c>
       <c r="F84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0113_01M_01M.27</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5585,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0450_01_1.50</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5890,7 +5890,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0310_00_G.02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5951,7 +5951,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0311_02_2.13</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6195,7 +6195,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0300_00_NG.03</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0113_00_G.10</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0103_01_1.B04</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0226_01_1.02</t>
+          <t>0005_00_G.01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 17:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6683,7 +6683,7 @@
         <v>50</v>
       </c>
       <c r="F105" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6988,7 +6988,7 @@
         <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0227_01_1.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7232,7 +7232,7 @@
         <v>13</v>
       </c>
       <c r="F114" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0131_04_4.07</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7293,7 +7293,7 @@
         <v>89</v>
       </c>
       <c r="F115" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0214_01_1.22</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0008_01_1.302</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0201_00_G.08</t>
+          <t>0201_00_G.06</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0228_07_7.01</t>
+          <t>0003_02_2.01</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0214_01_1.10</t>
+          <t>0227_02_2.39</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0450_04_4.35</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0210_-1_B.51-2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8147,7 +8147,7 @@
         <v>128</v>
       </c>
       <c r="F129" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8452,7 +8452,7 @@
         <v>8</v>
       </c>
       <c r="F134" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0227_03_3.54</t>
+          <t>0003_02_2.01</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 14:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8818,7 +8818,7 @@
         <v>80</v>
       </c>
       <c r="F140" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0113_01_1.416</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0113_02_2.27</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9123,7 +9123,7 @@
         <v>8</v>
       </c>
       <c r="F145" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0228_08_8.16</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9245,7 +9245,7 @@
         <v>35</v>
       </c>
       <c r="F147" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9289,12 +9289,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0003_02_2.01</t>
+          <t>0227_03_3.54</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9428,7 +9428,7 @@
         <v>8</v>
       </c>
       <c r="F150" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9550,7 +9550,7 @@
         <v>8</v>
       </c>
       <c r="F152" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0310_00_G.06</t>
+          <t>0201_01_1.02</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9611,7 +9611,7 @@
         <v>90</v>
       </c>
       <c r="F153" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0201_07_7.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0227_02_2.54</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="F156" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9838,12 +9838,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0228_02_2.18</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0103_01_1.B10</t>
+          <t>0113_00_G.204</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0110_02_2.01</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0003_01_1.05</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0335_03_3.3</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0113_00_G.12</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 13:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10953,7 +10953,7 @@
         <v>89</v>
       </c>
       <c r="F175" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0003_00_G.04</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0227_02_2.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0103_01_1.B15</t>
+          <t>0001_02_2.347</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11485,12 +11485,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11624,7 +11624,7 @@
         <v>8</v>
       </c>
       <c r="F186" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0254_01_1.10</t>
+          <t>0008_-1_B.152</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0254_01_1.07</t>
+          <t>0112_04_4.11</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0219_00_G.02</t>
+          <t>0008_00_G.251</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12173,7 +12173,7 @@
         <v>8</v>
       </c>
       <c r="F195" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -12217,12 +12217,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12234,7 +12234,7 @@
         <v>8</v>
       </c>
       <c r="F196" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0112_-1_B.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0201_05_5.05</t>
+          <t>0226_04_4.04</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12539,7 +12539,7 @@
         <v>52</v>
       </c>
       <c r="F201" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12644,12 +12644,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0335_01_1.3</t>
+          <t>0209_02_2.37</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12705,12 +12705,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0214_00_G.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12766,12 +12766,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12783,7 +12783,7 @@
         <v>8</v>
       </c>
       <c r="F205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -12827,12 +12827,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0008_00_G.251</t>
+          <t>0450_03_3.52</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0210_00_GFS2</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13132,12 +13132,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0335_01_1.1</t>
+          <t>0113_01M_01M.467</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13271,7 +13271,7 @@
         <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -13315,12 +13315,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0310_00_G.Z02</t>
+          <t>0227_00_G.04</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0335_02_2.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13620,12 +13620,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13759,7 +13759,7 @@
         <v>8</v>
       </c>
       <c r="F221" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0227_03_3.29</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13925,12 +13925,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 16:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -14047,12 +14047,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_01_1.16</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14125,7 +14125,7 @@
         <v>40</v>
       </c>
       <c r="F227" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -14169,12 +14169,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0283_01_1.20</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14247,7 +14247,7 @@
         <v>45</v>
       </c>
       <c r="F229" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14413,12 +14413,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14430,7 +14430,7 @@
         <v>8</v>
       </c>
       <c r="F232" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14596,12 +14596,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 17:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Thursday 15:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Wednesday 14:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0113_00_G.204</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -15084,12 +15084,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -15145,12 +15145,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -15162,7 +15162,7 @@
         <v>8</v>
       </c>
       <c r="F244" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -15206,12 +15206,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0008_01_1.306</t>
+          <t>0113_01M_01M.452</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15223,7 +15223,7 @@
         <v>80</v>
       </c>
       <c r="F245" t="n">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -15267,12 +15267,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0112_02_2.11</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0335_00_G.01</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15406,7 +15406,7 @@
         <v>120</v>
       </c>
       <c r="F248" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -15450,12 +15450,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0001_01_1.266</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0113_00_G.11</t>
+          <t>0008_-1_B.154</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Wednesday 11:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15633,12 +15633,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0201_04_4.14</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15877,12 +15877,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0228_11_11.11</t>
+          <t>0008_-1_B.153</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15938,12 +15938,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15955,7 +15955,7 @@
         <v>8</v>
       </c>
       <c r="F257" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 17:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -16060,12 +16060,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -16121,12 +16121,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16304,12 +16304,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16426,12 +16426,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16487,12 +16487,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16609,12 +16609,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16731,12 +16731,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16792,12 +16792,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16853,12 +16853,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16914,12 +16914,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -17219,12 +17219,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 16:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17358,7 +17358,7 @@
         <v>6</v>
       </c>
       <c r="F280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -17402,12 +17402,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17463,12 +17463,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>0227_03_3.14</t>
+          <t>0228_13_13.07</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17524,12 +17524,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17585,12 +17585,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17707,12 +17707,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 11:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -17724,7 +17724,7 @@
         <v>6</v>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0227_02_2.29</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 11:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17890,12 +17890,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0210_00_GFSSR2</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 16:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17907,7 +17907,7 @@
         <v>6</v>
       </c>
       <c r="F289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -17951,12 +17951,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -18012,12 +18012,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 10:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -18073,12 +18073,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18256,12 +18256,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18317,12 +18317,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18334,7 +18334,7 @@
         <v>6</v>
       </c>
       <c r="F296" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -18378,12 +18378,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18439,12 +18439,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Thursday 13:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">

--- a/multiSchoolOutput/04_School_of_Health_in_Social_Science/solution_weeks_9_10.xlsx
+++ b/multiSchoolOutput/04_School_of_Health_in_Social_Science/solution_weeks_9_10.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -857,12 +857,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1301,7 +1301,7 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0210_00_GFS1</t>
+          <t>0112_-1_B.02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1543,7 +1543,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0228_-1_LG.06</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1720,7 +1720,7 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0003_03_3.02</t>
+          <t>0208_-1_B.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1897,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0005_00_G.01</t>
+          <t>0335_05_5.3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2074,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0300_00_NG.01</t>
+          <t>0228_11_11.10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0335_01_1.16</t>
+          <t>0227_01_1.02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2192,7 +2192,7 @@
         <v>40</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2251,7 +2251,7 @@
         <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0227_00_G.02</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2310,7 +2310,7 @@
         <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0201_05_5.04</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2369,7 +2369,7 @@
         <v>40</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 11:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2428,7 +2428,7 @@
         <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0201_02_2.12</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2487,7 +2487,7 @@
         <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2546,7 +2546,7 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2605,7 +2605,7 @@
         <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0113_00_G.199</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2664,7 +2664,7 @@
         <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2782,7 +2782,7 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2841,7 +2841,7 @@
         <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 12:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2900,7 +2900,7 @@
         <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3018,7 +3018,7 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3077,7 +3077,7 @@
         <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0335_00_G.09</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3136,7 +3136,7 @@
         <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0110_02_2.04</t>
+          <t>0113_01_1.416</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3195,7 +3195,7 @@
         <v>40</v>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3254,7 +3254,7 @@
         <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3296,12 +3296,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0201_05_5.04</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3313,7 +3313,7 @@
         <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0228_-1_LG.11</t>
+          <t>0226_-1_LG.10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3372,7 +3372,7 @@
         <v>72</v>
       </c>
       <c r="F50" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113_00M_00M.05</t>
+          <t>0228_-1_LG.06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0226_04_4.04</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3490,7 +3490,7 @@
         <v>52</v>
       </c>
       <c r="F52" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3532,12 +3532,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0310_00_G.02</t>
+          <t>0113_01M_01M.469</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3549,7 +3549,7 @@
         <v>40</v>
       </c>
       <c r="F53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3608,7 +3608,7 @@
         <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3650,12 +3650,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3726,7 +3726,7 @@
         <v>6</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3768,12 +3768,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3785,7 +3785,7 @@
         <v>6</v>
       </c>
       <c r="F57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3827,12 +3827,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3844,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0001_01_1.275</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0008_03_3.451</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3962,7 +3962,7 @@
         <v>40</v>
       </c>
       <c r="F60" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Wednesday 15:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4021,7 +4021,7 @@
         <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0210_00_GFS1</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4139,7 +4139,7 @@
         <v>40</v>
       </c>
       <c r="F63" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 12:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4198,7 +4198,7 @@
         <v>80</v>
       </c>
       <c r="F64" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0450_01_1.40</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Tuesday 15:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4316,7 +4316,7 @@
         <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4375,7 +4375,7 @@
         <v>6</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 09:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4434,7 +4434,7 @@
         <v>6</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Friday 15:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4493,7 +4493,7 @@
         <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4535,12 +4535,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Thursday 14:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4552,7 +4552,7 @@
         <v>6</v>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0112_00_G.01</t>
+          <t>0112_00_G.02</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0228_-1_LG.11</t>
+          <t>0226_-1_LG.10</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4670,7 +4670,7 @@
         <v>72</v>
       </c>
       <c r="F72" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0005_00_G.01</t>
+          <t>0113_00_G.03</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4731,7 +4731,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4792,7 +4792,7 @@
         <v>8</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0008_03_3.451</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4853,7 +4853,7 @@
         <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4897,12 +4897,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0201_00_G.05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0003_00_G.03</t>
+          <t>0228_07_7.01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5158,7 +5158,7 @@
         <v>8</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0113_01_1.42</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5402,7 +5402,7 @@
         <v>8</v>
       </c>
       <c r="F84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0228_02_2.18</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5585,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0335_01_1.2</t>
+          <t>0227_00_G.05</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0450_01_1.50</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5890,7 +5890,7 @@
         <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5934,12 +5934,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0310_00_G.02</t>
+          <t>0335_03_3.2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5951,7 +5951,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0450_02_2.63</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0311_02_2.13</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6195,7 +6195,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0001_02_2.349</t>
+          <t>0001_02_2.351</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0113_02_2.65</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_02_2.14</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_07_7.01</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0005_00_G.01</t>
+          <t>0226_01_1.02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6683,7 +6683,7 @@
         <v>50</v>
       </c>
       <c r="F105" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0201_04_4.14</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6988,7 +6988,7 @@
         <v>8</v>
       </c>
       <c r="F110" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_02_2.3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0131_04_4.07</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Tuesday 16:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7293,7 +7293,7 @@
         <v>89</v>
       </c>
       <c r="F115" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0214_01_1.22</t>
+          <t>0003_01_1.05</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0008_01_1.302</t>
+          <t>0110_02_2.01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0008_00_G.267</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0003_02_2.01</t>
+          <t>0201_07_7.14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0227_02_2.39</t>
+          <t>0008_02_2.418</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0001_01_1.275</t>
+          <t>0008_00_G.267</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0008_02_2.403</t>
+          <t>0113_00_G.16</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0214_01_1.01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0210_-1_B.51-2</t>
+          <t>0450_02_2.35</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wednesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8147,7 +8147,7 @@
         <v>128</v>
       </c>
       <c r="F129" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -8191,12 +8191,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0113_00_G.16</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8374,12 +8374,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8452,7 +8452,7 @@
         <v>8</v>
       </c>
       <c r="F134" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0003_02_2.01</t>
+          <t>0227_03_3.39</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tuesday 14:00</t>
+          <t>Friday 14:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8818,7 +8818,7 @@
         <v>80</v>
       </c>
       <c r="F140" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0113_01_1.9</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0113_01_1.42</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0113_00_G.202B</t>
+          <t>0228_06_6.14</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0112_00_G.01</t>
+          <t>0112_00_G.02</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -9123,7 +9123,7 @@
         <v>8</v>
       </c>
       <c r="F145" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0228_08_8.13</t>
+          <t>0113_00_G.09</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0228_11_11.10</t>
+          <t>0112_-1_B.01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9245,7 +9245,7 @@
         <v>35</v>
       </c>
       <c r="F147" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -9289,12 +9289,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0450_03_3.62</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9428,7 +9428,7 @@
         <v>8</v>
       </c>
       <c r="F150" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0254_01_1.09</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9550,7 +9550,7 @@
         <v>8</v>
       </c>
       <c r="F152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0201_01_1.02</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 11:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9611,7 +9611,7 @@
         <v>90</v>
       </c>
       <c r="F153" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0227_03_3.39</t>
+          <t>0201_02_2.06</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9794,7 +9794,7 @@
         <v>8</v>
       </c>
       <c r="F156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0254_01_1.06</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9965,7 +9965,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10021,12 +10021,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>0335_05_5.1</t>
+          <t>0228_09_9.18</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -10082,12 +10082,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0254_01_1.06</t>
+          <t>0450_03_3.43</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0335_03_3.2</t>
+          <t>0311_01_1.26</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0113_00_G.203</t>
+          <t>0103_01_1.B10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -10326,12 +10326,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0450_03_3.63</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0228_06_6.10</t>
+          <t>0228_12_12.18</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -10570,12 +10570,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0201_00_G.06</t>
+          <t>0201_00_G.08</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0113_00_G.202B</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tuesday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0113_00_G.12</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Friday 13:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10753,12 +10753,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0112_-1_B.06</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0310_00_G.06</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Friday 16:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -10953,7 +10953,7 @@
         <v>89</v>
       </c>
       <c r="F175" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0113_01M_01M.20</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0228_06_6.10</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0001_02_2.347</t>
+          <t>0001_02_2.349</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wednesday 17:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>0112_-1_B.01</t>
+          <t>0113_00M_00M.05</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11485,12 +11485,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0113_01M_01M.467</t>
+          <t>0228_04_4.18</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0003_00_G.01</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0254_01_1.5A</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -11624,7 +11624,7 @@
         <v>8</v>
       </c>
       <c r="F186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0008_-1_B.152</t>
+          <t>0254_01_1.10</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0201_02_2.07</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_01_1.3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0112_04_4.11</t>
+          <t>0214_00_G.26</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Monday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0008_00_G.251</t>
+          <t>0112_-1_B.03</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Monday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0209_02_2.01</t>
+          <t>0226_-1_LG.19</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Friday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0001_00_G.158</t>
+          <t>0227_00_G.01</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -12173,7 +12173,7 @@
         <v>8</v>
       </c>
       <c r="F195" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -12217,12 +12217,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Monday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12234,7 +12234,7 @@
         <v>8</v>
       </c>
       <c r="F196" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>0201_01_1.05</t>
+          <t>0210_00_GFS2</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Thursday 12:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>0112_00_G.02</t>
+          <t>0112_00_G.01</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tuesday 12:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -12461,12 +12461,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0103_03_3.D02</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0226_04_4.04</t>
+          <t>0201_05_5.05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -12539,7 +12539,7 @@
         <v>52</v>
       </c>
       <c r="F201" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -12644,12 +12644,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>0209_02_2.37</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12705,12 +12705,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0113_01M_01M.469</t>
+          <t>0335_03_3.3</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12783,7 +12783,7 @@
         <v>8</v>
       </c>
       <c r="F205" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -12888,12 +12888,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0450_03_3.52</t>
+          <t>0201_02_2.05</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -12949,12 +12949,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0201_02_2.07</t>
+          <t>0103_01_1.B04</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>0001_02_2.351</t>
+          <t>0227_03_3.29</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -13271,7 +13271,7 @@
         <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0001_00_G.158</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13437,12 +13437,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0228_09_9.18</t>
+          <t>0335_05_5.1</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0450_03_3.42</t>
+          <t>0450_03_3.63</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -13620,12 +13620,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13759,7 +13759,7 @@
         <v>8</v>
       </c>
       <c r="F221" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0227_03_3.14</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13925,12 +13925,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0201_00_G.05</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0227_00_G.01</t>
+          <t>0335_04_4.1</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Wednesday 16:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -14047,12 +14047,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0201_01_1.01</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -14108,12 +14108,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0335_01_1.16</t>
+          <t>0214_00_G.02</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -14125,7 +14125,7 @@
         <v>40</v>
       </c>
       <c r="F227" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -14169,12 +14169,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0226_-1_LG.19</t>
+          <t>0209_02_2.01</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14230,12 +14230,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0283_01_1.20</t>
+          <t>0008_02_2.403</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Wednesday 09:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -14247,7 +14247,7 @@
         <v>45</v>
       </c>
       <c r="F229" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0450_01_1.63</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Wednesday 15:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0228_12_12.18</t>
+          <t>0113_01M_01M.19</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -14369,7 +14369,7 @@
         <v>13</v>
       </c>
       <c r="F231" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -14413,12 +14413,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0450_01_1.63</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Monday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -14430,7 +14430,7 @@
         <v>8</v>
       </c>
       <c r="F232" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -14474,12 +14474,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0003_00_G.01</t>
+          <t>0201_05_5.01</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0335_04_4.1</t>
+          <t>0450_04_4.35</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14596,12 +14596,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0214_01_1.01</t>
+          <t>0103_01_1.B19</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14718,12 +14718,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Tuesday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -14779,12 +14779,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0113_00_G.203</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Thursday 15:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>0254_01_1.5A</t>
+          <t>0450_03_3.42</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Wednesday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>0201_05_5.01</t>
+          <t>0201_01_1.01</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Monday 15:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -15084,12 +15084,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0113_00_G.199</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0450_02_2.63</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15162,7 +15162,7 @@
         <v>8</v>
       </c>
       <c r="F244" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -15206,12 +15206,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0113_01M_01M.452</t>
+          <t>0008_01_1.306</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -15223,7 +15223,7 @@
         <v>80</v>
       </c>
       <c r="F245" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -15267,12 +15267,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0112_02_2.11</t>
+          <t>0254_01_1.07</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0450_02_2.35</t>
+          <t>0335_00_G.01</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15406,7 +15406,7 @@
         <v>120</v>
       </c>
       <c r="F248" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Friday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15511,12 +15511,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0112_-1_B.06</t>
+          <t>0335_03_3.1</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Friday 14:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15572,12 +15572,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0008_-1_B.154</t>
+          <t>0201_05_5.07</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Wednesday 11:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Thursday 14:00</t>
+          <t>Tuesday 13:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15694,12 +15694,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>0103_01_1.B19</t>
+          <t>0201_01_1.05</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Friday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Friday 15:00</t>
+          <t>Monday 17:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Friday 09:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15877,12 +15877,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>0008_-1_B.153</t>
+          <t>0113_00_G.10</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15938,12 +15938,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0254_01_1.01</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15955,7 +15955,7 @@
         <v>8</v>
       </c>
       <c r="F257" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Thursday 17:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -16060,12 +16060,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -16121,12 +16121,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -16182,12 +16182,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 15:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16365,12 +16365,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16426,12 +16426,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -16487,12 +16487,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Wednesday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16670,12 +16670,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16792,12 +16792,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16853,12 +16853,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0227_03_3.30</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16914,12 +16914,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>0113_00M_00M.03</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_02_2.13</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -17097,12 +17097,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0113_01M_01M.474</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -17158,12 +17158,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0113_00M_00M.03</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -17219,12 +17219,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>0113_03_3.3</t>
+          <t>0227_02_2.30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -17280,12 +17280,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>0227_02_2.30</t>
+          <t>0210_00-GFSSR5</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Monday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17358,7 +17358,7 @@
         <v>6</v>
       </c>
       <c r="F280" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -17402,12 +17402,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_00M_00M.07</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17463,12 +17463,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>0228_13_13.07</t>
+          <t>0228_08_8.13</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Tuesday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17524,12 +17524,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -17585,12 +17585,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>0227_03_3.13</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Tuesday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17646,12 +17646,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>0254_01_1.12</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 14:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17707,12 +17707,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>0254_01_1.09</t>
+          <t>0210_00-GFSSR3</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Monday 11:00</t>
+          <t>Tuesday 12:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -17724,7 +17724,7 @@
         <v>6</v>
       </c>
       <c r="F286" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -17768,12 +17768,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_02M_02M.24</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>0227_02_2.29</t>
+          <t>0110_02_2.02</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Thursday 11:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -17890,12 +17890,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Thursday 16:00</t>
+          <t>Tuesday 09:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17907,7 +17907,7 @@
         <v>6</v>
       </c>
       <c r="F289" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -17951,12 +17951,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>0227_03_3.30</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -18012,12 +18012,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>0227_02_2.13</t>
+          <t>0113_03_3.3</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Thursday 10:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -18073,12 +18073,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>0113_02M_02M.24</t>
+          <t>0227_03_3.13</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Friday 11:00</t>
+          <t>Monday 12:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Thursday 12:00</t>
+          <t>Monday 09:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -18195,12 +18195,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>0214_00_G.23</t>
+          <t>0210_00-GFSSR4</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18256,12 +18256,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR4</t>
+          <t>0113_01M_01M.474</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18317,12 +18317,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>0254_01_1.01</t>
+          <t>0210_00_GFSSR2</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Tuesday 16:00</t>
+          <t>Tuesday 10:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18334,7 +18334,7 @@
         <v>6</v>
       </c>
       <c r="F296" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -18378,12 +18378,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>0210_00-GFSSR5</t>
+          <t>0214_00_G.23</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18439,12 +18439,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>0113_01_1.26</t>
+          <t>0254_01_1.12</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Thursday 09:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Thursday 13:00</t>
+          <t>Monday 10:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>0113_00M_00M.07</t>
+          <t>0113_01_1.26</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Wednesday 12:00</t>
+          <t>Monday 13:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
